--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3592-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3592-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43D38022-5C0A-453D-BFE5-FA6C431265D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B8F3139-2EDE-406A-90FF-A27729456F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{CA838495-8B88-451E-8814-C4C4F1792C3E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B51A777F-1646-4CCD-BE12-F65A0F44E9ED}"/>
   </bookViews>
   <sheets>
     <sheet name="3592-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1466,29 +1466,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD564B0-2528-4D04-BC10-CB093B76046F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D2E0C0-9979-4ED9-A49E-F185CB9D7EA3}">
   <dimension ref="A1:X23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.625" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +1521,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1558,7 +1557,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1610,7 +1609,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1678,7 +1677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1750,7 +1749,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1822,7 +1821,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1894,7 +1893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1966,7 +1965,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2110,7 +2109,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2254,7 +2253,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2326,7 +2325,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2398,7 +2397,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2470,7 +2469,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2542,7 +2541,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2614,7 +2613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2686,7 +2685,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2758,7 +2757,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2830,7 +2829,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2902,7 +2901,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -2974,7 +2973,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
         <v>46</v>
       </c>
